--- a/release/v2026.4.0/StructureDefinition-mii-pr-pro-observation-eq5d5l-vas.xlsx
+++ b/release/v2026.4.0/StructureDefinition-mii-pr-pro-observation-eq5d5l-vas.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.2.0</t>
+    <t>2026.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-14T19:09:51+00:00</t>
+    <t>2026-06-14T19:15:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/release/v2026.4.0/StructureDefinition-mii-pr-pro-observation-eq5d5l-vas.xlsx
+++ b/release/v2026.4.0/StructureDefinition-mii-pr-pro-observation-eq5d5l-vas.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-14T19:15:38+00:00</t>
+    <t>2026-06-14T19:29:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/release/v2026.4.0/StructureDefinition-mii-pr-pro-observation-eq5d5l-vas.xlsx
+++ b/release/v2026.4.0/StructureDefinition-mii-pr-pro-observation-eq5d5l-vas.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-14T19:29:08+00:00</t>
+    <t>2026-06-14T19:52:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/release/v2026.4.0/StructureDefinition-mii-pr-pro-observation-eq5d5l-vas.xlsx
+++ b/release/v2026.4.0/StructureDefinition-mii-pr-pro-observation-eq5d5l-vas.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.4.0</t>
+    <t>2026.4.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-14T19:52:10+00:00</t>
+    <t>2026-06-15T12:51:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
